--- a/config/excel/CfgRunPersistence.xlsx
+++ b/config/excel/CfgRunPersistence.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CfgRunPersistence" sheetId="1" r:id="Ra369c82f2f364e56"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CfgRunPersistence" sheetId="1" r:id="R459c3c115cab40c9"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -13,28 +13,19 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="4">
+  <x:fonts count="2">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
     </x:font>
     <x:font>
-      <x:sz val="10"/>
-      <x:name val="Microsoft YaHei"/>
-    </x:font>
-    <x:font>
       <x:b/>
-      <x:sz val="10"/>
+      <x:sz val="11"/>
       <x:color rgb="FFFFFFFF"/>
-      <x:name val="Microsoft YaHei"/>
-    </x:font>
-    <x:font>
-      <x:sz val="10"/>
-      <x:color rgb="FF0000FF"/>
-      <x:name val="Microsoft YaHei"/>
+      <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="5">
+  <x:fills count="3">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -46,34 +37,23 @@
         <x:fgColor rgb="FF17365D"/>
       </x:patternFill>
     </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFDBEAF7"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFFFF2CC"/>
-      </x:patternFill>
-    </x:fill>
   </x:fills>
   <x:borders count="1">
-    <x:border/>
+    <x:border>
+      <x:left/>
+      <x:right/>
+      <x:top/>
+      <x:bottom/>
+      <x:diagonal/>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="8">
+  <x:cellXfs count="3">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -275,79 +255,55 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
-  <x:cols>
-    <x:col min="1" max="1" width="20" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="20" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="20" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="20" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="20" hidden="0" customWidth="1"/>
-  </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="32" customHeight="1">
-      <x:c r="A1" s="3" t="str">
+    <x:row r="1">
+      <x:c r="A1" s="2" t="str">
         <x:v>ID</x:v>
       </x:c>
-      <x:c r="B1" s="3" t="str">
+      <x:c r="B1" s="2" t="str">
         <x:v>ConfigVersion</x:v>
       </x:c>
-      <x:c r="C1" s="3" t="str">
+      <x:c r="C1" s="2" t="str">
         <x:v>CheckpointTicks</x:v>
       </x:c>
-      <x:c r="D1" s="3" t="str">
+      <x:c r="D1" s="2" t="str">
         <x:v>MaxPendingTicks</x:v>
       </x:c>
-      <x:c r="E1" s="3" t="str">
+      <x:c r="E1" s="2" t="str">
         <x:v>MaxStateBytes</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" ht="24" customHeight="1">
-      <x:c r="A2" s="4" t="str">
+    <x:row r="2">
+      <x:c r="A2" t="str">
         <x:v>int</x:v>
       </x:c>
-      <x:c r="B2" s="4" t="str">
+      <x:c r="B2" t="str">
         <x:v>string</x:v>
       </x:c>
-      <x:c r="C2" s="4" t="str">
+      <x:c r="C2" t="str">
         <x:v>int</x:v>
       </x:c>
-      <x:c r="D2" s="4" t="str">
+      <x:c r="D2" t="str">
         <x:v>int</x:v>
       </x:c>
-      <x:c r="E2" s="4" t="str">
+      <x:c r="E2" t="str">
         <x:v>int</x:v>
       </x:c>
     </x:row>
-    <x:row r="3" ht="42" customHeight="1">
-      <x:c r="A3" s="6" t="str">
-        <x:v># 保存规则编号</x:v>
-      </x:c>
-      <x:c r="B3" s="6" t="str">
-        <x:v>运行配置版本</x:v>
-      </x:c>
-      <x:c r="C3" s="6" t="str">
-        <x:v>检查点最大增量数</x:v>
-      </x:c>
-      <x:c r="D3" s="6" t="str">
-        <x:v>待确认逻辑帧预算</x:v>
-      </x:c>
-      <x:c r="E3" s="6" t="str">
-        <x:v>完整快照字节上限</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" ht="24" customHeight="1">
-      <x:c r="A4" s="7" t="n">
+    <x:row r="3">
+      <x:c r="A3" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="B4" s="7" t="str">
-        <x:v>v2-content-1</x:v>
-      </x:c>
-      <x:c r="C4" s="7" t="n">
+      <x:c r="B3" t="str">
+        <x:v>v3-room-prototype-1</x:v>
+      </x:c>
+      <x:c r="C3" t="n">
         <x:v>120</x:v>
       </x:c>
-      <x:c r="D4" s="7" t="n">
+      <x:c r="D3" t="n">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="E4" s="7" t="n">
+      <x:c r="E3" t="n">
         <x:v>8388608</x:v>
       </x:c>
     </x:row>

--- a/config/excel/CfgRunPersistence.xlsx
+++ b/config/excel/CfgRunPersistence.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CfgRunPersistence" sheetId="1" r:id="R459c3c115cab40c9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CfgRunPersistence" sheetId="1" r:id="R65856da21b9f452d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -13,29 +13,18 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="2">
+  <x:fonts count="1">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
     </x:font>
-    <x:font>
-      <x:b/>
-      <x:sz val="11"/>
-      <x:color rgb="FFFFFFFF"/>
-      <x:name val="Carlito"/>
-    </x:font>
   </x:fonts>
-  <x:fills count="3">
+  <x:fills count="2">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="gray125"/>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FF17365D"/>
-      </x:patternFill>
     </x:fill>
   </x:fills>
   <x:borders count="1">
@@ -50,10 +39,8 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="3">
+  <x:cellXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -257,19 +244,19 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="2" t="str">
+      <x:c r="A1" t="str">
         <x:v>ID</x:v>
       </x:c>
-      <x:c r="B1" s="2" t="str">
+      <x:c r="B1" t="str">
         <x:v>ConfigVersion</x:v>
       </x:c>
-      <x:c r="C1" s="2" t="str">
+      <x:c r="C1" t="str">
         <x:v>CheckpointTicks</x:v>
       </x:c>
-      <x:c r="D1" s="2" t="str">
+      <x:c r="D1" t="str">
         <x:v>MaxPendingTicks</x:v>
       </x:c>
-      <x:c r="E1" s="2" t="str">
+      <x:c r="E1" t="str">
         <x:v>MaxStateBytes</x:v>
       </x:c>
     </x:row>
@@ -295,7 +282,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B3" t="str">
-        <x:v>v3-room-prototype-1</x:v>
+        <x:v>v3-room-prototype-2</x:v>
       </x:c>
       <x:c r="C3" t="n">
         <x:v>120</x:v>

--- a/config/excel/CfgRunPersistence.xlsx
+++ b/config/excel/CfgRunPersistence.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CfgRunPersistence" sheetId="1" r:id="R65856da21b9f452d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CfgRunPersistence" sheetId="1" r:id="R4d7f01486292413a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -282,7 +282,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B3" t="str">
-        <x:v>v3-room-prototype-2</x:v>
+        <x:v>v3-room-prototype-3</x:v>
       </x:c>
       <x:c r="C3" t="n">
         <x:v>120</x:v>
